--- a/shipping_rates_norway_raw_data.xlsx
+++ b/shipping_rates_norway_raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\Documents\GitHub Projects\shipping_rates_norway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B78FA79-CF19-4C23-AFFF-EF67C40E994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1C7676-B3C2-4506-9AB7-FD1EBEA3FE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
     <sheet name="Lookups" sheetId="3" r:id="rId3"/>
     <sheet name="Output" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6432" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6439" uniqueCount="688">
   <si>
     <t>OceanSwift</t>
   </si>
@@ -2072,6 +2085,21 @@
   </si>
   <si>
     <t>High cube addon</t>
+  </si>
+  <si>
+    <t>48 USD</t>
+  </si>
+  <si>
+    <t>53 USD</t>
+  </si>
+  <si>
+    <t>55 USD</t>
+  </si>
+  <si>
+    <t>All rates exclude both origin and destination Terminal Handling Charges (THC), and hence, the THC Methodology used is "NONE", except for the rates where the destination port is Bergen or Brevik.</t>
+  </si>
+  <si>
+    <t>Where the destination port is Bergen or Brevik, rates have destination Terminal Handling Charge included, and hence, the THC Methodology used is "DTHC".</t>
   </si>
 </sst>
 </file>
@@ -2414,7 +2442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -4535,20 +4563,20 @@
       <c r="B59" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="E59">
-        <v>48</v>
-      </c>
-      <c r="H59">
-        <v>48</v>
-      </c>
-      <c r="K59">
-        <v>53</v>
-      </c>
-      <c r="N59">
-        <v>53</v>
-      </c>
-      <c r="Q59">
-        <v>55</v>
+      <c r="E59" t="s">
+        <v>683</v>
+      </c>
+      <c r="H59" t="s">
+        <v>683</v>
+      </c>
+      <c r="K59" t="s">
+        <v>684</v>
+      </c>
+      <c r="N59" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -4764,6 +4792,16 @@
       </c>
       <c r="Q68" t="s">
         <v>589</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/shipping_rates_norway_raw_data.xlsx
+++ b/shipping_rates_norway_raw_data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\Documents\GitHub Projects\shipping_rates_norway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1C7676-B3C2-4506-9AB7-FD1EBEA3FE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292158A2-4EBE-4B70-92A6-6CC8833B657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Input" sheetId="1" r:id="rId1"/>
-    <sheet name="Volume" sheetId="2" r:id="rId2"/>
-    <sheet name="Lookups" sheetId="3" r:id="rId3"/>
-    <sheet name="Output" sheetId="4" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="5" r:id="rId1"/>
+    <sheet name="Input" sheetId="1" r:id="rId2"/>
+    <sheet name="Volume" sheetId="2" r:id="rId3"/>
+    <sheet name="Lookups" sheetId="3" r:id="rId4"/>
+    <sheet name="Output" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6439" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6454" uniqueCount="703">
   <si>
     <t>OceanSwift</t>
   </si>
@@ -2096,18 +2097,86 @@
     <t>55 USD</t>
   </si>
   <si>
-    <t>All rates exclude both origin and destination Terminal Handling Charges (THC), and hence, the THC Methodology used is "NONE", except for the rates where the destination port is Bergen or Brevik.</t>
-  </si>
-  <si>
-    <t>Where the destination port is Bergen or Brevik, rates have destination Terminal Handling Charge included, and hence, the THC Methodology used is "DTHC".</t>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Transform the rates in the "Input" tab to the format in the "Output" tab.</t>
+  </si>
+  <si>
+    <t>For allocation of volumes, only rates that are actually valid at date should get volume allocated.</t>
+  </si>
+  <si>
+    <t>Tabs' Details</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Rows 4 - 56 contains rates from different global ports to Oslo.</t>
+  </si>
+  <si>
+    <t>Whenever the cost is marked as "N/A", there is no service to the final destination and no rate should be calculated to this destination.</t>
+  </si>
+  <si>
+    <t>Rows 63 - 68 specifies the Transport Additionals at Destination (TADs) related to the dataset (The additional cost for transporting the container from Oslo to the smaller ports in Norway):</t>
+  </si>
+  <si>
+    <t>Whenever the cost is marked as "0", there is no additional cost.</t>
+  </si>
+  <si>
+    <t>Whenever a cost is specified, add the TAD to the rate for World - Oslo in order to reflect the full traderoute.</t>
+  </si>
+  <si>
+    <t>The Terminal Handling Charges (THC) method for Bergen and Brevik ports is "DTHC" and, for other ports, it is "NONE".</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Volume for a specific set of port-to-port combinations, freight forwarders and equipments during current date range.</t>
+  </si>
+  <si>
+    <t>Lookups</t>
+  </si>
+  <si>
+    <t>Links the port name with its code.</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Displays the valid shipping rates with equipment type per column (to do).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2135,11 +2204,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2441,8 +2514,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{346BC19A-3EED-4DE9-8CBF-A879FDEE16D1}">
+  <dimension ref="B2:D23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C9" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C10" s="5" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C11" s="5"/>
+      <c r="D11" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D12" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D13" s="3" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="5" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -4794,22 +4963,12 @@
         <v>589</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
-        <v>687</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F1856"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41939,7 +42098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -42437,7 +42596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
